--- a/artfynd/A 47097-2024 artfynd.xlsx
+++ b/artfynd/A 47097-2024 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>136258844</v>
       </c>
       <c r="B3" t="n">
-        <v>102649</v>
+        <v>102652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47097-2024 artfynd.xlsx
+++ b/artfynd/A 47097-2024 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>136258844</v>
       </c>
       <c r="B3" t="n">
-        <v>102652</v>
+        <v>102653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47097-2024 artfynd.xlsx
+++ b/artfynd/A 47097-2024 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>136258844</v>
       </c>
       <c r="B3" t="n">
-        <v>102653</v>
+        <v>102658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47097-2024 artfynd.xlsx
+++ b/artfynd/A 47097-2024 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>136258844</v>
       </c>
       <c r="B3" t="n">
-        <v>102658</v>
+        <v>102660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
